--- a/data/trans_camb/P16-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,81</t>
+          <t>6,81; 15,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 11,94</t>
+          <t>2,64; 11,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,02</t>
+          <t>4,68; 14,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,04</t>
+          <t>5,49; 11,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,76</t>
+          <t>4,9; 11,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,11</t>
+          <t>3,69; 9,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,31</t>
+          <t>7,33; 12,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,77</t>
+          <t>5,45; 10,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,13</t>
+          <t>5,63; 11,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 25,23</t>
+          <t>10,99; 26,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 20,48</t>
+          <t>4,27; 20,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 23,35</t>
+          <t>7,54; 25,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,19</t>
+          <t>7,11; 15,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 15,91</t>
+          <t>6,36; 15,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,48</t>
+          <t>4,77; 13,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 18,05</t>
+          <t>10,33; 18,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 15,85</t>
+          <t>7,74; 15,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,27</t>
+          <t>7,89; 16,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 15,07</t>
+          <t>8,75; 15,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 17,2</t>
+          <t>10,55; 17,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 19,56</t>
+          <t>-1,18; 19,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 19,07</t>
+          <t>11,85; 18,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,87</t>
+          <t>7,9; 14,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 26,96</t>
+          <t>11,62; 27,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 16,03</t>
+          <t>10,86; 15,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 15,23</t>
+          <t>10,29; 14,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 21,21</t>
+          <t>5,68; 21,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,55; 52,58</t>
+          <t>27,39; 52,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,6; 60,02</t>
+          <t>33,1; 59,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 65,97</t>
+          <t>-3,18; 65,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,62; 43,26</t>
+          <t>24,34; 42,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,02; 34,13</t>
+          <t>16,37; 33,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,16; 59,48</t>
+          <t>24,43; 61,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,24; 43,61</t>
+          <t>27,57; 42,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 41,87</t>
+          <t>26,03; 40,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 56,02</t>
+          <t>15,64; 56,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 14,04</t>
+          <t>0,74; 14,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 17,48</t>
+          <t>5,35; 17,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,32; 25,2</t>
+          <t>12,66; 25,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,17</t>
+          <t>0,01; 13,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 10,59</t>
+          <t>-2,24; 10,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 12,37</t>
+          <t>1,28; 12,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,72</t>
+          <t>3,26; 12,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,13</t>
+          <t>4,03; 12,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,83</t>
+          <t>9,42; 18,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 45,93</t>
+          <t>1,95; 47,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 57,68</t>
+          <t>14,57; 58,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,41; 81,64</t>
+          <t>33,77; 81,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 29,43</t>
+          <t>0,2; 29,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 22,13</t>
+          <t>-4,06; 21,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 25,98</t>
+          <t>2,3; 27,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 31,87</t>
+          <t>7,53; 31,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 33,26</t>
+          <t>9,14; 32,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,1; 45,75</t>
+          <t>21,2; 46,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,16</t>
+          <t>7,48; 12,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,59</t>
+          <t>6,7; 11,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 13,62</t>
+          <t>-1,84; 13,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 13,84</t>
+          <t>9,2; 13,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,84</t>
+          <t>3,81; 8,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,08</t>
+          <t>4,09; 13,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,91; 12,51</t>
+          <t>9,08; 12,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,58</t>
+          <t>6,0; 9,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,35</t>
+          <t>1,41; 11,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,55; 31,18</t>
+          <t>17,96; 31,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,04; 29,64</t>
+          <t>16,23; 29,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 34,08</t>
+          <t>-4,48; 33,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 24,13</t>
+          <t>15,41; 24,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,5</t>
+          <t>6,35; 15,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 24,14</t>
+          <t>6,9; 23,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,59; 25,54</t>
+          <t>17,81; 25,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,65; 19,61</t>
+          <t>11,98; 19,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 25,09</t>
+          <t>2,76; 24,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>6,71</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,28</t>
+          <t>6,72; 15,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,97</t>
+          <t>2,93; 11,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 14,72</t>
+          <t>1,94; 12,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 11,7</t>
+          <t>5,61; 11,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,32</t>
+          <t>5,09; 11,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,89</t>
+          <t>2,89; 9,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,36</t>
+          <t>7,42; 12,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,69</t>
+          <t>5,13; 10,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,07</t>
+          <t>3,54; 9,3</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 26,0</t>
+          <t>10,67; 25,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 20,32</t>
+          <t>4,61; 19,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 25,2</t>
+          <t>3,12; 20,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 15,83</t>
+          <t>7,27; 15,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,21</t>
+          <t>6,45; 15,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 13,22</t>
+          <t>3,7; 12,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,09</t>
+          <t>10,54; 18,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 15,6</t>
+          <t>7,21; 15,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 16,09</t>
+          <t>4,91; 13,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>17,73</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,86</t>
+          <t>11,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,18</t>
+          <t>14,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 15,18</t>
+          <t>8,52; 15,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,05</t>
+          <t>10,68; 17,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 19,57</t>
+          <t>14,81; 21,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 18,82</t>
+          <t>12,49; 19,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 14,69</t>
+          <t>7,86; 14,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 27,68</t>
+          <t>7,93; 14,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,86; 15,76</t>
+          <t>10,8; 15,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,94</t>
+          <t>10,15; 14,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 21,29</t>
+          <t>12,63; 17,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,39; 52,96</t>
+          <t>26,23; 54,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,1; 59,42</t>
+          <t>33,41; 61,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 65,17</t>
+          <t>46,17; 73,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,34; 42,35</t>
+          <t>26,05; 44,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 33,25</t>
+          <t>16,43; 33,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,43; 61,92</t>
+          <t>16,36; 33,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 42,81</t>
+          <t>27,19; 42,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,03; 40,67</t>
+          <t>25,95; 40,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 56,7</t>
+          <t>32,02; 46,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,18</t>
+          <t>19,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,73</t>
+          <t>13,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 14,19</t>
+          <t>1,22; 14,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 17,65</t>
+          <t>5,22; 17,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 25,08</t>
+          <t>13,77; 25,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 13,96</t>
+          <t>1,04; 14,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 10,28</t>
+          <t>-1,76; 10,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,85</t>
+          <t>1,72; 13,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,65</t>
+          <t>3,21; 12,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,68</t>
+          <t>3,63; 12,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 18,06</t>
+          <t>9,68; 17,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 47,09</t>
+          <t>3,42; 45,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,57; 58,39</t>
+          <t>14,11; 57,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,77; 81,91</t>
+          <t>37,51; 83,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 29,7</t>
+          <t>1,96; 31,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 21,79</t>
+          <t>-3,39; 23,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 27,38</t>
+          <t>3,16; 27,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 31,97</t>
+          <t>7,54; 32,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 32,1</t>
+          <t>8,01; 32,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,2; 46,15</t>
+          <t>22,12; 45,45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>11,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,33</t>
+          <t>8,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,45</t>
+          <t>7,43; 12,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,55</t>
+          <t>6,87; 11,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 13,49</t>
+          <t>9,32; 14,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,91</t>
+          <t>9,37; 13,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,74</t>
+          <t>3,7; 8,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,65</t>
+          <t>2,57; 7,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,08; 12,48</t>
+          <t>9,13; 12,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,35</t>
+          <t>6,13; 9,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,93</t>
+          <t>6,61; 10,1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,96; 31,75</t>
+          <t>17,74; 31,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,23; 29,47</t>
+          <t>16,38; 29,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 33,66</t>
+          <t>22,2; 36,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,41; 24,23</t>
+          <t>15,71; 24,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 15,22</t>
+          <t>6,17; 15,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,9; 23,54</t>
+          <t>4,38; 12,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,81; 25,47</t>
+          <t>18,07; 25,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,16</t>
+          <t>12,02; 19,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 24,22</t>
+          <t>13,1; 20,66</t>
         </is>
       </c>
     </row>
